--- a/isolated_excel/Serial Correlation Diagnostics.xlsx
+++ b/isolated_excel/Serial Correlation Diagnostics.xlsx
@@ -443,7 +443,7 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.3518264189608743</v>
+        <v>0.3509970274106829</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.0001322452612779038</v>
+        <v>0.0001284846804513028</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5.670595079073489e-05</v>
+        <v>6.361355649042701e-05</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>6.444721769888872e-05</v>
+        <v>0.0001080691514194616</v>
       </c>
     </row>
     <row r="3">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.140188581203098</v>
+        <v>-0.1408993197056948</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.1277568081678591</v>
+        <v>0.1242446882228043</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.4457248592970162</v>
+        <v>0.4275470952219309</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.3066839911331234</v>
+        <v>0.2921222183482972</v>
       </c>
     </row>
     <row r="4">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.01465478878200355</v>
+        <v>0.01354931980108134</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.8735038164340262</v>
+        <v>0.8824833815391561</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.9787208520808429</v>
+        <v>0.9765260962819015</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.8799447076786946</v>
+        <v>0.904341090705725</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +582,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Jul 2026; 115 monthly observations</t>
+          <t>Jan 2017 to Aug 2026; 116 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Serial Correlation Diagnostics.xlsx
+++ b/isolated_excel/Serial Correlation Diagnostics.xlsx
@@ -444,7 +444,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.3509970274106829</v>
+        <v>0.352906727312786</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.0001284846804513028</v>
+        <v>0.0001104917251849064</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>6.361355649042701e-05</v>
+        <v>6.775773678677842e-05</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.0001080691514194616</v>
+        <v>0.0001573140187863196</v>
       </c>
     </row>
     <row r="3">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.1408993197056948</v>
+        <v>-0.141745700150389</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.1242446882228043</v>
+        <v>0.1204437627181503</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.4275470952219309</v>
+        <v>0.4242018367818284</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.2921222183482972</v>
+        <v>0.2865737320015871</v>
       </c>
     </row>
     <row r="4">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.01354931980108134</v>
+        <v>0.01420447443690255</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.8824833815391561</v>
+        <v>0.8763333571020252</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.9765260962819015</v>
+        <v>0.9764233648274664</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.904341090705725</v>
+        <v>0.9051211984022886</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +582,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Aug 2026; 116 monthly observations</t>
+          <t>Jan 2017 to Sept 2026; 117 monthly observations</t>
         </is>
       </c>
     </row>
